--- a/test-data/students-level-courses.xlsx
+++ b/test-data/students-level-courses.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Roster" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,7 +446,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1001 انجل, 1202 تقن</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1103 احص, 1203 نهج</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2310 ويب, 2311 ويب</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>441234570</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2410 ويب, 2412 ويب</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>441234571</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3510 ويب, 3511 ويب</t>
         </is>
       </c>
     </row>
